--- a/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0001T0006Z000C1N75_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0001T0006Z000C1N75_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>38.97727885864162</v>
+        <v>6.333807814529263</v>
       </c>
       <c r="D2" t="n">
-        <v>38.91827521442813</v>
+        <v>6.324219722344571</v>
       </c>
       <c r="E2" t="n">
-        <v>2.858359185337159</v>
+        <v>0.4644833676172884</v>
       </c>
       <c r="F2" t="n">
-        <v>12.6781827912625</v>
+        <v>2.060204703580156</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>36.7257156832719</v>
+        <v>5.967928798531684</v>
       </c>
       <c r="D3" t="n">
-        <v>21.62270612384914</v>
+        <v>3.513689745125485</v>
       </c>
       <c r="E3" t="n">
-        <v>2.858359185337159</v>
+        <v>0.4644833676172884</v>
       </c>
       <c r="F3" t="n">
-        <v>12.6781827912625</v>
+        <v>2.060204703580156</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>42.69318948602013</v>
+        <v>6.937643291478271</v>
       </c>
       <c r="D4" t="n">
-        <v>12.85883389544107</v>
+        <v>2.089560508009174</v>
       </c>
       <c r="E4" t="n">
-        <v>2.858359185337159</v>
+        <v>0.4644833676172884</v>
       </c>
       <c r="F4" t="n">
-        <v>12.6781827912625</v>
+        <v>2.060204703580156</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>43.86510853934995</v>
+        <v>7.128080137644367</v>
       </c>
       <c r="D5" t="n">
-        <v>44.17333464708167</v>
+        <v>7.178166880150771</v>
       </c>
       <c r="E5" t="n">
-        <v>2.858359185337159</v>
+        <v>0.4644833676172884</v>
       </c>
       <c r="F5" t="n">
-        <v>12.6781827912625</v>
+        <v>2.060204703580156</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
